--- a/data/trans_dic/P1417-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1417-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,07</t>
+          <t>0,16; 1,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,78</t>
+          <t>0,32; 2,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,58</t>
+          <t>0,97; 4,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,55</t>
+          <t>2,32; 5,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,89</t>
+          <t>0,25; 1,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,18</t>
+          <t>0,64; 2,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,44</t>
+          <t>0,12; 1,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,85</t>
+          <t>1,3; 2,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,18</t>
+          <t>0,24; 2,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,01</t>
+          <t>0,25; 1,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,95</t>
+          <t>0,56; 3,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,64</t>
+          <t>0,92; 4,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,12</t>
+          <t>2,24; 5,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,75</t>
+          <t>0,29; 1,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,09</t>
+          <t>0,42; 2,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,02</t>
+          <t>0,5; 1,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,8</t>
+          <t>1,3; 2,96</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,76</t>
+          <t>0,15; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,16</t>
+          <t>0,37; 2,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,26</t>
+          <t>0,69; 2,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,55</t>
+          <t>1,24; 7,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,24</t>
+          <t>0,72; 4,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,28</t>
+          <t>1,88; 8,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,78</t>
+          <t>2,61; 7,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,43</t>
+          <t>0,59; 2,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,4</t>
+          <t>0,22; 1,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,14</t>
+          <t>0,9; 3,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,02</t>
+          <t>1,44; 3,5</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,28</t>
+          <t>0,26; 1,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,08</t>
+          <t>0,91; 2,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,3</t>
+          <t>0,58; 2,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,53</t>
+          <t>1,36; 3,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,51</t>
+          <t>1,44; 3,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,44</t>
+          <t>2,31; 4,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,99</t>
+          <t>0,28; 0,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,83</t>
+          <t>0,82; 1,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,75</t>
+          <t>0,8; 1,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,46</t>
+          <t>1,65; 2,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,95</t>
+          <t>0,51; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,96</t>
+          <t>0,19; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,4</t>
+          <t>0,14; 1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,72</t>
+          <t>1,42; 3,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,79</t>
+          <t>1,0; 3,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,29</t>
+          <t>2,84; 6,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,84</t>
+          <t>2,86; 5,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,46</t>
+          <t>5,24; 8,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,68</t>
+          <t>1,04; 2,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,04</t>
+          <t>2,04; 4,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,54</t>
+          <t>1,75; 3,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,63</t>
+          <t>4,0; 5,96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,27 +1437,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,79</t>
+          <t>1,2; 2,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,46</t>
+          <t>1,56; 3,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,93</t>
+          <t>1,18; 3,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,22</t>
+          <t>3,37; 6,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,2</t>
+          <t>0,93; 2,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,49</t>
+          <t>0,98; 2,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,41</t>
+          <t>2,67; 4,73</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,69</t>
+          <t>0,22; 0,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,72</t>
+          <t>0,27; 0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,86</t>
+          <t>0,34; 0,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,44</t>
+          <t>0,93; 1,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,21</t>
+          <t>1,32; 2,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,34</t>
+          <t>2,22; 3,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,98</t>
+          <t>1,96; 3,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,86</t>
+          <t>3,92; 5,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,36</t>
+          <t>0,85; 1,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,93</t>
+          <t>1,3; 1,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,06</t>
+          <t>2,56; 3,22</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19997</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 10816</t>
+          <t>0; 9617</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6275</t>
+          <t>0; 7133</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5897</t>
+          <t>0; 5653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>339; 5428</t>
+          <t>864; 7589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>957; 8522</t>
+          <t>975; 7737</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3040; 14393</t>
+          <t>3049; 14174</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 9781</t>
+          <t>0; 11709</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11131; 24820</t>
+          <t>11337; 25752</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2036; 14765</t>
+          <t>1989; 14866</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4821; 16364</t>
+          <t>4818; 17782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>903; 11188</t>
+          <t>906; 12280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12800; 27183</t>
+          <t>13530; 28662</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>17959</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4184</t>
+          <t>0; 5448</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 5113</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>902; 8206</t>
+          <t>907; 9011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1070; 9089</t>
+          <t>1192; 8915</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1966; 10960</t>
+          <t>2093; 11848</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3201; 15684</t>
+          <t>3126; 14475</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1900; 10902</t>
+          <t>1894; 10902</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8117; 19562</t>
+          <t>9457; 21330</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2178; 12933</t>
+          <t>2114; 13081</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3939; 15841</t>
+          <t>3155; 16786</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3913; 15118</t>
+          <t>3751; 14824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10373; 23359</t>
+          <t>11813; 26804</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>15471</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>818; 9545</t>
+          <t>814; 10057</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5256</t>
+          <t>0; 5284</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1816; 11296</t>
+          <t>1930; 11866</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1374; 15070</t>
+          <t>3239; 13350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2084; 12663</t>
+          <t>2087; 12939</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1905; 11037</t>
+          <t>1878; 10983</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3106; 13748</t>
+          <t>3115; 13365</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4334; 12969</t>
+          <t>4885; 14285</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4571; 17256</t>
+          <t>4164; 17118</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2042; 12481</t>
+          <t>1979; 12315</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6874; 21624</t>
+          <t>6196; 21456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5525; 25117</t>
+          <t>9446; 23007</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37766</t>
+          <t>42515</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7110</t>
+          <t>0; 6767</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3112; 14880</t>
+          <t>3067; 13966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1922; 10991</t>
+          <t>1923; 11028</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8554; 21507</t>
+          <t>10252; 23619</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3931; 16464</t>
+          <t>4173; 15822</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10332; 26986</t>
+          <t>10428; 27278</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11180; 28960</t>
+          <t>11904; 29417</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10869; 33556</t>
+          <t>19883; 36260</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5398; 19261</t>
+          <t>5427; 18575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15586; 35224</t>
+          <t>15748; 35490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15688; 34632</t>
+          <t>15849; 35010</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25714; 49405</t>
+          <t>32861; 53440</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>55884</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>68679</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1720; 10332</t>
+          <t>1775; 11187</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1001; 10005</t>
+          <t>982; 9688</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>894; 8671</t>
+          <t>895; 8875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6617; 17565</t>
+          <t>8002; 20916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6004; 21536</t>
+          <t>5707; 20059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22481; 47838</t>
+          <t>21564; 47785</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21494; 43147</t>
+          <t>21104; 43204</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36241; 62523</t>
+          <t>43407; 67904</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8509; 24635</t>
+          <t>9562; 26267</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24457; 51340</t>
+          <t>25970; 51701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24378; 48111</t>
+          <t>23725; 47127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>46913; 73703</t>
+          <t>55779; 83044</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>38414</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6294</t>
+          <t>0; 7097</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15189; 34884</t>
+          <t>14925; 35033</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17238; 38305</t>
+          <t>17326; 38699</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12481; 31666</t>
+          <t>12820; 32527</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28370; 54871</t>
+          <t>28402; 51637</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14539; 34103</t>
+          <t>14372; 34611</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17345; 38671</t>
+          <t>17378; 38659</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15124; 34053</t>
+          <t>13399; 34302</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27788; 54139</t>
+          <t>28854; 51043</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>147850</t>
+          <t>160999</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>185111</t>
+          <t>203033</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7319; 22521</t>
+          <t>7192; 22185</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9037; 24533</t>
+          <t>9086; 24518</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11754; 29059</t>
+          <t>11543; 28679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26493; 48551</t>
+          <t>32125; 55050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43663; 74685</t>
+          <t>44752; 73864</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>78163; 118567</t>
+          <t>78838; 117618</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>69071; 105327</t>
+          <t>69298; 106722</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>119619; 173339</t>
+          <t>142275; 183489</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>56261; 90494</t>
+          <t>56389; 90892</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>91497; 134784</t>
+          <t>90484; 134727</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85568; 127291</t>
+          <t>85742; 127297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>155946; 212619</t>
+          <t>180988; 227319</t>
         </is>
       </c>
     </row>
